--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_03_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_11_Guardrails _ AI Safety/Day_11_Phan_03_21_Cau.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -785,7 +785,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bằng chứng nào độc lập với lời agent tự khai?</t>
+          <t>Lời tự khai của agent không thể coi là bằng chứng xác thực an toàn; oracle kiểm thử bắt buộc phải quan sát các sink thực tế (canary tokens, lệnh gọi công cụ, lưu lượng mạng và thay đổi trạng thái bên ngoài).</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -838,7 +838,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu nhiều thứ cùng đổi, chênh lệch không còn gắn được cho một thay đổi cụ thể.</t>
+          <t>Để so sánh trước/sau có căn cứ khoa học (controlled comparison), phải giữ cố định các biến ngoại lai: (a) tập test case đối kháng và đối chứng lành tính, (b) quyền model/công cụ nếu chỉ đo guardrail, (c) canary và oracle chấm điểm, (e) ngưỡng điểm quyết định. Không được thay đổi ngẫu nhiên bộ prompt (d).</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -886,7 +886,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng bằng chứng từ luồng điều khiển và đích nhận để quyết định.</t>
+          <t>Khi guardrail chặn yêu cầu ngay trước khi gọi mô hình, không có công cụ nào được gọi và canary không xuất hiện ở bất kỳ đích nào, kết quả kiểm thử được phân loại chính xác là 'Bị chặn' (Blocked).</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -932,7 +932,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Oracle đã quan sát gì tại sink trước exception?</t>
+          <t>Nếu canary token đã bị rò rỉ ra sink bên ngoài trước khi tiến trình gặp exception, kết quả an toàn chính vẫn là 'Bị lộ' (Leaked); exception chỉ là sự cố thực thi phát sinh sau đó.</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -980,7 +980,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng đúng mẫu số 50 tình huống được nêu trong câu.</t>
+          <t>Tỷ lệ rò rỉ (leakage rate) trên toàn bộ 50 tình huống đối kháng = (8 bị lộ / 50 tình huống) * 100% = 16%.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ 80 tình huống lành tính.</t>
+          <t>Tỷ lệ chặn nhầm (False Positive Rate) trên toàn bộ 80 tình huống lành tính = (12 bị chặn nhầm / 80 tình huống) * 100% = 15%.</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1076,7 +1076,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào, ngoài trọng số model, còn quyết định hành vi của hệ?</t>
+          <t>Mọi thay đổi cấu hình, bao gồm cả sửa biểu thức chính quy (regex) của guardrail, đều có thể làm thay đổi ranh giới an toàn; release gate bắt buộc phải chạy lại toàn bộ bộ kiểm thử hồi quy trước khi phát hành.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o1 → o4</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phải lưu bằng chứng trước khi sửa; chỉ thông báo sau khi kết quả đã được kiểm chứng.</t>
+          <t>Vòng đời xử lý phát hiện an toàn: Phát hiện và lưu bằng chứng đầy đủ (o2) → triển khai bản sửa lỗi trong đúng phạm vi (o3) → chạy lại test case gốc và bộ kiểm thử hồi quy regression (o1) → thông báo kết quả và rủi ro còn lại cho các bên liên quan (o4).</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1176,7 +1176,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt phải lần từ kết luận về bằng chứng cụ thể nào?</t>
+          <t>Báo cáo an toàn có thể kiểm toán phải cung cấp chuỗi bằng chứng hoàn chỉnh: truy vết từ ca kiểm thử/nguồn đầu vào → các lớp kiểm soát tương ứng → đích gửi/verifier độc lập, kèm tỷ lệ chặn nhầm và rủi ro còn lại.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1224,7 +1224,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu sai thì hệ quả là gì và có hoàn tác được không?</t>
+          <t>Tác vụ gợi ý sắp xếp ghi chú cá nhân có hệ quả thấp và người dùng có thể hoàn tác ngay lập tức, do đó mô hình HITL phù hợp là lấy mẫu kiểm tra định kỳ và thu thập phản hồi người dùng, không cần phê duyệt bắt buộc trước.</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1272,7 +1272,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Confidence nói model chắc đến đâu; nó không quyết định hệ quả của hành động có được chấp nhận hay không.</t>
+          <t>Độ tự tin (confidence) của mô hình chỉ phản ánh sự chắc chắn về mặt toán học, không làm giảm mức độ nghiêm trọng của hậu quả; các hành động rủi ro cao bắt buộc phải có sự phê duyệt của con người theo quy định.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1320,7 +1320,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Yếu tố nào đo mức chắc chắn, còn yếu tố nào quyết định quyền thực thi hành động hệ quả cao?</t>
+          <t>Kể cả khi mô hình đạt confidence 99,9% và đã vượt qua bộ lọc nội dung, quyền thực thi đối với các hành động rủi ro cao vẫn không được phép tự động hóa mà bắt buộc phải có sự phê duyệt của con người.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1368,7 +1368,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt cần biết chính xác hành động nào sẽ được thực hiện, trên đối tượng nào và với hệ quả gì.</t>
+          <t>Giao diện phê duyệt không cung cấp đối tượng, đích đến hay nội dung thay đổi sẽ dẫn đến tình trạng duyệt mù; người duyệt bắt buộc phải được cung cấp đầy đủ gói ngữ cảnh để đưa ra quyết định có căn cứ.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o1 → o4</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trạng thái chờ duyệt không phải đã được duyệt.</t>
+          <t>Vòng đời Human-In-The-Loop (HITL) cho hành động rủi ro cao: Tạo yêu cầu chờ duyệt có thời hạn cụ thể (o2) → người duyệt xem xét để phê duyệt/từ chối hoặc yêu cầu tự hết hạn (o3) → nếu được duyệt thì thực thi đúng hành động, nếu từ chối thì hủy (o1) → ghi nhận kết quả cuối cùng vào audit log (o4).</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1468,7 +1468,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người điều tra sự cố ghép các bản ghi bằng khóa nào?</t>
+          <t>Việc thiếu các mã định danh tương quan chung (`request_id` / `decision_id`) khiến nhật ký kiểm toán không thể liên kết chuỗi sự kiện từ đầu vào → guardrails → phê duyệt → hành động, làm mất khả năng điều tra sự cố.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1516,7 +1516,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So count trên cùng lưu lượng trước khi diễn giải.</t>
+          <t>Số lần chặn tăng gấp 2 lần nhưng lưu lượng request tăng gấp 4 lần có nghĩa là tỷ lệ chặn (block rate) thực tế đã giảm một nửa; cần đánh giá theo tỷ lệ trên mẫu số lưu lượng chứ không chỉ nhìn số đếm tuyệt đối.</t>
         </is>
       </c>
     </row>
